--- a/都更全案投報_對照範本.xlsx
+++ b/都更全案投報_對照範本.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>黃底=輸入(只改這)｜白底=自動算｜D欄貼你舊Excel對應值｜E欄=差異(&gt;±2%留意)｜範例＝中正段</t>
+          <t>黃底=輸入(只改這)｜白底=自動算｜D欄貼你舊Excel對應值｜E欄=差異(&gt;±2%留意)｜範例＝合成案例C</t>
         </is>
       </c>
     </row>
@@ -1556,19 +1556,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>安和段估價師送審試算：營造22萬·設計監造5%·營業稅5%·印花0.1%</t>
+          <t>真實案估價師送審試算（私有校準）：營造22萬·營業稅5%·印花0.1%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>住宅單價(中正段)</t>
+          <t>住宅單價(合成案例C)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中正紀念堂周邊新案 120–162萬/坪，4M巷取保守 130萬（2026-06查證）</t>
+          <t>依區位行情帶入；合成示範值 136萬/坪</t>
         </is>
       </c>
     </row>
